--- a/PICHINCHA/Octubre/PICHINCHA-Octubre.xlsx
+++ b/PICHINCHA/Octubre/PICHINCHA-Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B051D42A-08B8-4C20-9284-C038A6D83691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF21A5ED-9BC0-41B6-AF9E-1632D101FD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
   <si>
     <t>UF</t>
   </si>
@@ -208,9 +208,6 @@
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
     <t>GABRIEL</t>
   </si>
   <si>
@@ -253,40 +250,34 @@
     <t>SEGURO DE VIDA. SRA MONICA GOROSITO</t>
   </si>
   <si>
-    <t>Vto. 15/10</t>
-  </si>
-  <si>
-    <t>Liquidacion mes de SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>TSG - MES DE SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>ARTICULOS DE LIMPIEZA</t>
   </si>
   <si>
     <t>TSG</t>
   </si>
   <si>
-    <t>Septiembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agosto </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASA RUAN COMPRA DE MATERIALES </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERVISUR - COLOCACION DE PLAFONES Y SENSORES </t>
-  </si>
-  <si>
-    <t>Mes de septiembre NO abonado</t>
-  </si>
-  <si>
-    <t>Mes de agosto NO abonado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESTAPACION 04/09 </t>
+    <t>Vto. 14/11</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>OCTUBRE</t>
+  </si>
+  <si>
+    <t>Mes de OCTUBRE NO abonado</t>
+  </si>
+  <si>
+    <t>Mes de SEPTIEMBRE NO abonado</t>
+  </si>
+  <si>
+    <t>DESTAPACION AYSA 31/10</t>
+  </si>
+  <si>
+    <t>ELECTROTEL - CONFIRGURACION DE CAMARAS</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1314,6 +1305,8 @@
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1383,8 +1376,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1752,7 +1743,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1804,10 +1795,10 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="111" t="s">
         <v>76</v>
-      </c>
-      <c r="F7" s="111" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1830,47 +1821,47 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="123" t="s">
+      <c r="E11" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="123"/>
+      <c r="F11" s="125"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="108"/>
       <c r="C12" s="122">
-        <v>16955.79</v>
+        <v>17651.48</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="56" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <v>-551011.45319646737</v>
+        <v>-488188.33730846737</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="107" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C13" s="122">
         <v>0</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="147"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="124"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="122">
-        <v>92086</v>
+        <v>119977</v>
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="58" t="s">
@@ -1878,7 +1869,7 @@
       </c>
       <c r="F14" s="59">
         <f>'prorrateo '!F10</f>
-        <v>813424.68588800007</v>
+        <v>713925.33753599995</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1886,29 +1877,27 @@
         <v>19</v>
       </c>
       <c r="B15" s="108" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15" s="80">
-        <v>33600</v>
+        <v>40000</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="58" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="59">
-        <f>-(C45)</f>
-        <v>-750601.57000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <f>-(C41)</f>
+        <v>-629935.84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="108" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="80">
-        <v>33600</v>
+        <v>71</v>
+      </c>
+      <c r="B16" s="108"/>
+      <c r="C16" s="120">
+        <v>50000</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="58"/>
@@ -1916,11 +1905,11 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B17" s="108"/>
       <c r="C17" s="120">
-        <v>56653.99</v>
+        <v>125989</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
@@ -1928,11 +1917,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="108"/>
+        <v>69</v>
+      </c>
+      <c r="B18" s="108" t="s">
+        <v>79</v>
+      </c>
       <c r="C18" s="120">
-        <v>103185.38</v>
+        <v>0</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="58"/>
@@ -1940,13 +1931,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="108" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C19" s="120">
-        <v>0</v>
+        <v>56212.61</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="58"/>
@@ -1954,10 +1942,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" s="120">
-        <v>51725.66</v>
+        <v>15103</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="58"/>
@@ -1965,67 +1953,68 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="120">
-        <v>15344</v>
-      </c>
-      <c r="D21" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="C21" s="120"/>
       <c r="E21" s="58"/>
       <c r="F21" s="59"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="108"/>
-      <c r="C22" s="120">
-        <v>14248</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="59"/>
+      <c r="H21" s="108"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="87">
+        <f>SUM(C12:C21)</f>
+        <v>424933.08999999997</v>
+      </c>
+      <c r="E22" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="119">
+        <f>SUM(F12:F21)</f>
+        <v>-404198.83977246739</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="120"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="59"/>
-      <c r="H23" s="108"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="87">
-        <f>SUM(C12:C23)</f>
-        <v>417398.82000000007</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="119">
-        <f>SUM(F12:F23)</f>
-        <v>-488188.33730846737</v>
-      </c>
+      <c r="A23" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="113"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="120">
+        <v>71833</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="113"/>
+      <c r="A25" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="120">
+        <v>4519.75</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B26" s="35"/>
       <c r="C26" s="120">
-        <v>71833</v>
+        <v>78650</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="19"/>
@@ -2033,23 +2022,23 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B27" s="35"/>
       <c r="C27" s="120">
-        <v>4519.75</v>
+        <v>50000</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="35"/>
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="128"/>
       <c r="C28" s="120">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="19"/>
@@ -2057,213 +2046,188 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B29" s="35"/>
-      <c r="C29" s="120">
-        <v>39000</v>
+      <c r="C29" s="112">
+        <f>750601.57-629935.84</f>
+        <v>120665.72999999998</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="120">
-        <v>115000</v>
+      <c r="A30" s="32"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="109">
+        <f>SUM(C23:C29)</f>
+        <v>325668.47999999998</v>
       </c>
       <c r="D30" s="5"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="120">
-        <v>50000</v>
+      <c r="A31" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49">
+        <f>+C30+C22</f>
+        <v>750601.57</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="19"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="125" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="126"/>
-      <c r="C32" s="120">
-        <v>36350</v>
-      </c>
-      <c r="D32" s="5"/>
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="82"/>
+      <c r="C32" s="83"/>
       <c r="E32" s="19"/>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="112"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="20"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="109">
-        <f>SUM(C25:C33)</f>
-        <v>333202.75</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="49">
-        <f>+C34+C24</f>
-        <v>750601.57000000007</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="20"/>
-    </row>
-    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69" t="s">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="82"/>
-      <c r="C36" s="83"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="20"/>
-    </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="54"/>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="54"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="52"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="53">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="61"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="53">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="78"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="81"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="78"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="86"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="52"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="53">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="78"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="81">
         <v>0</v>
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="61"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="53">
-        <v>0</v>
-      </c>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="78"/>
-      <c r="B41" s="79"/>
-      <c r="C41" s="81"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="64"/>
+      <c r="C40" s="65">
+        <f>SUM(C35:C39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="53">
+        <f>C31-C29</f>
+        <v>629935.84</v>
+      </c>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="78"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="86"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="77">
+        <f>+C31</f>
+        <v>750601.57</v>
+      </c>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="78"/>
-      <c r="B43" s="84"/>
-      <c r="C43" s="81">
-        <v>0</v>
-      </c>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="64"/>
-      <c r="C44" s="65">
-        <f>SUM(C39:C43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="53">
-        <f>C35-C33</f>
-        <v>750601.57000000007</v>
-      </c>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C46" s="77">
-        <f>+C35</f>
-        <v>750601.57000000007</v>
-      </c>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="63" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="65">
-        <f>+C35+C44</f>
-        <v>750601.57000000007</v>
-      </c>
-      <c r="E47" s="16"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D52" s="6"/>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="124"/>
-      <c r="C54" s="124"/>
-      <c r="D54" s="124"/>
-      <c r="E54" s="124"/>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="124"/>
-      <c r="C55" s="124"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="124"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="124"/>
-      <c r="C56" s="124"/>
-      <c r="D56" s="124"/>
-      <c r="E56" s="124"/>
+      <c r="B43" s="64"/>
+      <c r="C43" s="65">
+        <f>+C31+C40</f>
+        <v>750601.57</v>
+      </c>
+      <c r="E43" s="16"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="126"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="126"/>
+      <c r="C51" s="126"/>
+      <c r="D51" s="126"/>
+      <c r="E51" s="126"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="126"/>
+      <c r="C52" s="126"/>
+      <c r="D52" s="126"/>
+      <c r="E52" s="126"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="19"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="20"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="19"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="18"/>
-      <c r="C68" s="20"/>
+      <c r="C68" s="18"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
@@ -2280,31 +2244,11 @@
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="18"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B54:E56"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B50:E52"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2364,7 +2308,7 @@
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de SEPTIEMBRE</v>
+        <v>Liquidacion mes de OCTUBRE</v>
       </c>
       <c r="B2" s="73"/>
       <c r="C2" s="73"/>
@@ -2416,10 +2360,10 @@
         <v>38</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2450,10 +2394,10 @@
       </c>
       <c r="L4" s="66" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 15/10</v>
+        <v>Vto. 14/11</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2464,22 +2408,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="41">
-        <v>207196.89868800002</v>
+        <v>156338.09218094082</v>
       </c>
       <c r="F5" s="80">
-        <v>207000</v>
+        <v>100000</v>
       </c>
       <c r="G5" s="67">
         <f>E5-F5</f>
-        <v>196.89868800001568</v>
+        <v>56338.092180940817</v>
       </c>
       <c r="H5" s="70">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>7.8759475200006275</v>
+        <v>2253.5236872376327</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2494,11 +2438,11 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>150325.08863552002</v>
+        <v>208711.92986817847</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>156338.09218094082</v>
+        <v>217060.40706290561</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2509,22 +2453,23 @@
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="41">
-        <v>101567.10720000001</v>
+        <v>151750.10548800003</v>
       </c>
       <c r="F6" s="80">
-        <v>100000</v>
+        <f>E6</f>
+        <v>151750.10548800003</v>
       </c>
       <c r="G6" s="67">
         <f>E6-F6</f>
-        <v>1567.1072000000131</v>
+        <v>0</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ref="H6:H9" si="0">IF(G6&gt;0,G6*4%,0)</f>
-        <v>62.684288000000528</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -2539,11 +2484,11 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>151750.10548800003</v>
+        <v>150120.31400000001</v>
       </c>
       <c r="M6" s="39">
         <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>157820.10970752002</v>
+        <v>156125.12656</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2554,23 +2499,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="41">
-        <v>207196.89868800002</v>
+        <v>156125.12656</v>
       </c>
       <c r="F7" s="80">
-        <f t="shared" ref="F7:F9" si="3">E7</f>
-        <v>207196.89868800002</v>
+        <v>154300</v>
       </c>
       <c r="G7" s="67">
-        <f t="shared" ref="G7:G8" si="4">E7-F7</f>
-        <v>0</v>
+        <f t="shared" ref="G7:G8" si="3">E7-F7</f>
+        <v>1825.1265600000042</v>
       </c>
       <c r="H7" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>73.00506240000017</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2585,11 +2529,11 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>150120.31400000001</v>
+        <v>152018.44562240003</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="2"/>
-        <v>156125.12656</v>
+        <v>158099.18344729603</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2600,18 +2544,18 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
-        <v>199227.78720000002</v>
+        <v>156125.12656</v>
       </c>
       <c r="F8" s="80">
+        <f>E8</f>
+        <v>156125.12656</v>
+      </c>
+      <c r="G8" s="67">
         <f t="shared" si="3"/>
-        <v>199227.78720000002</v>
-      </c>
-      <c r="G8" s="67">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H8" s="70">
@@ -2646,22 +2590,23 @@
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="41">
-        <v>101567.10720000001</v>
+        <v>151750.10548800003</v>
       </c>
       <c r="F9" s="80">
-        <v>100000</v>
+        <f>E9</f>
+        <v>151750.10548800003</v>
       </c>
       <c r="G9" s="67">
         <f>E9-F9</f>
-        <v>1567.1072000000131</v>
+        <v>0</v>
       </c>
       <c r="H9" s="70">
         <f t="shared" si="0"/>
-        <v>62.684288000000528</v>
+        <v>0</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
@@ -2676,11 +2621,11 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>151750.10548800003</v>
+        <v>150120.31400000001</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" si="2"/>
-        <v>157820.10970752002</v>
+        <v>156125.12656</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2690,111 +2635,111 @@
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="45">
-        <f t="shared" ref="D10:M10" si="5">SUM(D5:D9)</f>
+        <f t="shared" ref="D10:M10" si="4">SUM(D5:D9)</f>
         <v>0</v>
       </c>
       <c r="E10" s="42">
-        <f t="shared" si="5"/>
-        <v>816755.79897600005</v>
+        <f t="shared" si="4"/>
+        <v>772088.55627694097</v>
       </c>
       <c r="F10" s="42">
         <f>SUM(F5:F9)</f>
-        <v>813424.68588800007</v>
+        <v>713925.33753599995</v>
       </c>
       <c r="G10" s="50">
-        <f t="shared" si="5"/>
-        <v>3331.1130880000419</v>
+        <f t="shared" si="4"/>
+        <v>58163.218740940822</v>
       </c>
       <c r="H10" s="50">
-        <f t="shared" si="5"/>
-        <v>133.24452352000168</v>
+        <f t="shared" si="4"/>
+        <v>2326.5287496376327</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>750601.57000000007</v>
       </c>
       <c r="K10" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L10" s="118">
-        <f t="shared" si="5"/>
-        <v>754065.92761152005</v>
+        <f t="shared" si="4"/>
+        <v>811091.31749057851</v>
       </c>
       <c r="M10" s="118">
-        <f t="shared" si="5"/>
-        <v>784228.5647159809</v>
+        <f t="shared" si="4"/>
+        <v>843534.97019020165</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="128"/>
-      <c r="L14" s="128"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="128"/>
-      <c r="L15" s="128"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="128"/>
-      <c r="J16" s="128"/>
-      <c r="K16" s="128"/>
-      <c r="L16" s="128"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2816,60 +2761,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="136"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="140">
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142">
         <v>565</v>
       </c>
-      <c r="E2" s="141"/>
+      <c r="E2" s="143"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="142" t="s">
+      <c r="A3" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="144" t="s">
+      <c r="D3" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="E3" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="129" t="s">
+      <c r="F3" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="129" t="s">
+      <c r="G3" s="131" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="143"/>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="145"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
@@ -3029,11 +2974,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="131"/>
-      <c r="B12" s="132"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="133"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Octubre/PICHINCHA-Octubre.xlsx
+++ b/PICHINCHA/Octubre/PICHINCHA-Octubre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF21A5ED-9BC0-41B6-AF9E-1632D101FD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9478EBCC-AB94-49F2-B7A7-60016DEB1421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -250,9 +250,6 @@
     <t>SEGURO DE VIDA. SRA MONICA GOROSITO</t>
   </si>
   <si>
-    <t>ARTICULOS DE LIMPIEZA</t>
-  </si>
-  <si>
     <t>TSG</t>
   </si>
   <si>
@@ -278,6 +275,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>CAMBIO DE AUTOMATICO - SR. JULIO</t>
   </si>
 </sst>
 </file>
@@ -1795,10 +1795,10 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1847,7 +1847,7 @@
         <v>65</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" s="122">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="108" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="80">
         <v>40000</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="F15" s="59">
         <f>-(C41)</f>
-        <v>-629935.84</v>
+        <v>-739935.84</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1920,7 +1920,7 @@
         <v>69</v>
       </c>
       <c r="B18" s="108" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="120">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="120">
         <v>15103</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="F22" s="119">
         <f>SUM(F12:F21)</f>
-        <v>-404198.83977246739</v>
+        <v>-514198.83977246739</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2010,7 +2010,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="35"/>
       <c r="C26" s="120">
@@ -2022,7 +2022,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="35"/>
       <c r="C27" s="120">
@@ -2034,11 +2034,11 @@
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="127" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B28" s="128"/>
       <c r="C28" s="120">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="19"/>
@@ -2062,7 +2062,7 @@
       <c r="B30" s="33"/>
       <c r="C30" s="109">
         <f>SUM(C23:C29)</f>
-        <v>325668.47999999998</v>
+        <v>435668.47999999998</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -2076,7 +2076,7 @@
       <c r="B31" s="48"/>
       <c r="C31" s="49">
         <f>+C30+C22</f>
-        <v>750601.57</v>
+        <v>860601.57</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="19"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C41" s="53">
         <f>C31-C29</f>
-        <v>629935.84</v>
+        <v>739935.84</v>
       </c>
       <c r="F41" s="6"/>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C42" s="77">
         <f>+C31</f>
-        <v>750601.57</v>
+        <v>860601.57</v>
       </c>
       <c r="F42" s="6"/>
     </row>
@@ -2175,7 +2175,7 @@
       <c r="B43" s="64"/>
       <c r="C43" s="65">
         <f>+C31+C40</f>
-        <v>750601.57</v>
+        <v>860601.57</v>
       </c>
       <c r="E43" s="16"/>
     </row>
@@ -2300,7 +2300,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="71">
-        <v>750601.57000000007</v>
+        <v>860601.57</v>
       </c>
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="J5" s="38">
         <f>K$1/5</f>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="K5" s="117">
         <f>K2*D5</f>
@@ -2438,11 +2438,11 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>208711.92986817847</v>
+        <v>230711.92986817844</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>217060.40706290561</v>
+        <v>239940.40706290558</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="J6" s="38">
         <f t="shared" ref="J6:J9" si="1">K$1/5</f>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="K6" s="117">
         <f>K2*D6</f>
@@ -2484,11 +2484,11 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="M6" s="39">
         <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>156125.12656</v>
+        <v>179005.12655999998</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="J7" s="38">
         <f t="shared" si="1"/>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="K7" s="117">
         <f>K2*D7</f>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>152018.44562240003</v>
+        <v>174018.4456224</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="2"/>
-        <v>158099.18344729603</v>
+        <v>180979.183447296</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2544,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="J8" s="38">
         <f t="shared" si="1"/>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="K8" s="117">
         <f>K2*D8</f>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="2"/>
-        <v>156125.12656</v>
+        <v>179005.12655999998</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="J9" s="38">
         <f t="shared" si="1"/>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="K9" s="117">
         <f>K2*D9</f>
@@ -2621,11 +2621,11 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>150120.31400000001</v>
+        <v>172120.31399999998</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" si="2"/>
-        <v>156125.12656</v>
+        <v>179005.12655999998</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J10" s="46">
         <f t="shared" si="4"/>
-        <v>750601.57000000007</v>
+        <v>860601.57</v>
       </c>
       <c r="K10" s="46">
         <f t="shared" si="4"/>
@@ -2668,11 +2668,11 @@
       </c>
       <c r="L10" s="118">
         <f t="shared" si="4"/>
-        <v>811091.31749057851</v>
+        <v>921091.31749057851</v>
       </c>
       <c r="M10" s="118">
         <f t="shared" si="4"/>
-        <v>843534.97019020165</v>
+        <v>957934.97019020154</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
